--- a/projects/xiuxian/game/data/table/事件配置.xlsx
+++ b/projects/xiuxian/game/data/table/事件配置.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -648,31 +648,271 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>__sys_extraction__</t>
+          <t>exp_herb_field</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>撤离历练</t>
+          <t>灵草秘园</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>历练结束，收获归宗。</t>
+          <t>一片隐蔽的山谷里长满了各色灵草，灵气扑面而来。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>system</t>
+          <t>treasure</t>
         </is>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
+        <v>35</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>exp_old_hermit</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>山中隐者</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>一位白发老者在溪边垂钓，见你来到，微微一笑。</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>encounter</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="F9" t="n">
+        <v>25</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>exp_spirit_spring</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>灵泉涌动</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>一汪清泉从石缝中涌出，泉水蕴含精纯灵气。</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>treasure</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>30</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>exp_ruins_choice</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>古修遗府</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>一座坍塌的洞府半掩在藤蔓之下，似有传承，亦有禁制。</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>trial</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>45</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>show_options</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>exp_wandering_cultivator</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>散修问道</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>一名散修拦路，要与你切磋一番，赌注是身上的灵石。</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>battle</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>35</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>exp_poison_swamp</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>瘴气沼泽</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>前方是一片散发着紫色瘴气的沼泽，强行通过会损耗灵石。</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>story</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>25</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>exp_demon_ambush</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>妖群围攻</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>三只金瞳妖豹从林中扑出，将你团团围住！</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>battle</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>40</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>群战</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>exp_treasure_vault</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>秘境宝库</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>秘境深处的宝库大门虚掩，里面金光闪烁。</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>treasure</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>35</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>__sys_extraction__</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>撤离历练</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>历练结束，收获归宗。</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>system</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>系统保留</t>
         </is>
@@ -689,7 +929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1560,12 +1800,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>sys_ext_1</t>
+          <t>exp_herb_field_1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>__sys_extraction__</t>
+          <t>exp_herb_field</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1579,7 +1819,7 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>带着此行收获，你踏上了归宗之路。</t>
+          <t>你小心采撷，收获颇丰。</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1589,7 +1829,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>sys_ext_2</t>
+          <t>exp_herb_field_2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -1598,14 +1838,1119 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>extraction</t>
+          <t>give_resource</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>spirit_herb</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>exp_old_hermit_1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>exp_old_hermit</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>show_text</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>老者道：'年轻人，可愿与我手谈一局？'</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>exp_old_hermit_2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>show_options</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>opt_hermit_learn</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>opt_hermit_gift</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>exp_old_hermit_3</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>show_text</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>flag('choice') == 'opt_hermit_learn'</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>老者指点了你几句修行心得，令你受益匪浅。</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>exp_old_hermit_4</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="n">
+        <v>4</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>give_resource</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>flag('choice') == 'opt_hermit_learn'</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>spirit_stone</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>exp_old_hermit_5</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>show_text</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>flag('choice') == 'opt_hermit_gift'</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>老者赠你一袋灵草，飘然而去。</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>exp_old_hermit_6</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="n">
+        <v>6</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>give_resource</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>flag('choice') == 'opt_hermit_gift'</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>spirit_herb</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>exp_spirit_spring_1</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>exp_spirit_spring</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>show_text</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>你掬一捧泉水饮下，灵气在经脉中流转，神清气爽。</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>exp_spirit_spring_2</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>give_resource</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>spirit_stone</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>exp_ruins_choice_1</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>exp_ruins_choice</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>show_text</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>洞府禁制隐隐发光，强闯有风险，但传承诱人。</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>exp_ruins_choice_2</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>show_options</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>opt_ruins_force</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>opt_ruins_careful</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>exp_ruins_choice_3</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>show_text</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>flag('choice') == 'opt_ruins_force'</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>你强行破禁，触发了守护傀儡！</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>exp_ruins_choice_4</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>start_battle</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>flag('choice') == 'opt_ruins_force'</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>foundation</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>exp_ruins_choice_5</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>show_text</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>flag('battle_result') == 'win'</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>傀儡崩解，你取得了洞府中的宝物！</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>exp_ruins_choice_6</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="n">
+        <v>6</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>give_resource</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>flag('battle_result') == 'win'</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>spirit_stone</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>exp_ruins_choice_7</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="n">
+        <v>7</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>give_resource</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>flag('battle_result') == 'win'</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>demon_core</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>exp_ruins_choice_8</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="n">
+        <v>8</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>show_text</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>flag('battle_result') == 'lose'</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>傀儡太强，你只得退走。</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>exp_ruins_choice_9</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="n">
+        <v>9</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>show_text</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>flag('choice') == 'opt_ruins_careful'</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>你只取了外围零散之物，安全离开。</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>exp_ruins_choice_10</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="n">
+        <v>10</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>give_resource</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>flag('choice') == 'opt_ruins_careful'</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>spirit_herb</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>exp_wandering_cultivator_1</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>exp_wandering_cultivator</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>show_text</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>散修抱拳：'得罪了！'</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>exp_wandering_cultivator_2</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>start_battle</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>qi</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>exp_wandering_cultivator_3</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>show_text</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>flag('battle_result') == 'win'</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>散修认输，留下灵石悻悻离去。</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>exp_wandering_cultivator_4</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="n">
+        <v>4</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>give_resource</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>flag('battle_result') == 'win'</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>spirit_stone</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>exp_wandering_cultivator_5</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="n">
+        <v>5</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>show_text</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>flag('battle_result') == 'lose'</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>你技不如人，丢了些灵石。</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>exp_wandering_cultivator_6</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="n">
+        <v>6</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>give_resource</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>flag('battle_result') == 'lose'</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>spirit_stone</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-150</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>exp_poison_swamp_1</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>exp_poison_swamp</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>show_text</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>你运转灵力抵御瘴气，勉强通过，消耗不小。</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>exp_poison_swamp_2</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>give_resource</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>spirit_stone</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-100</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>exp_demon_ambush_1</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>exp_demon_ambush</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>show_text</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>三只金瞳妖豹气势汹汹！</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>exp_demon_ambush_2</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>start_battle</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>golden</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>exp_demon_ambush_3</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>show_text</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>flag('battle_result') == 'win'</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>妖豹尽数倒地，妖丹收入囊中！</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>exp_demon_ambush_4</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr"/>
+      <c r="C61" t="n">
+        <v>4</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>give_resource</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>flag('battle_result') == 'win'</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>demon_core</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>exp_demon_ambush_5</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="n">
+        <v>5</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>show_text</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>flag('battle_result') == 'lose'</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>寡不敌众，你负伤撤退。</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>exp_demon_ambush_6</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
+      <c r="C63" t="n">
+        <v>6</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>extraction</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>flag('battle_result') == 'lose'</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>exp_treasure_vault_1</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>exp_treasure_vault</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>show_text</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>宝库中珍宝琳琅满目，你满载而归！</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>exp_treasure_vault_2</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>give_resource</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>spirit_stone</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>exp_treasure_vault_3</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="n">
+        <v>3</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>give_resource</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>millennium_herb</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>sys_ext_1</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>__sys_extraction__</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>show_text</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>带着此行收获，你踏上了归宗之路。</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>sys_ext_2</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr"/>
+      <c r="C68" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>extraction</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1618,7 +2963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1753,6 +3098,106 @@
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>opt_hermit_learn</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>请教修行</t>
+        </is>
+      </c>
+      <c r="C5" t="b">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>opt_hermit_gift</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>讨要灵草</t>
+        </is>
+      </c>
+      <c r="C6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>opt_ruins_force</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>强闯洞府</t>
+        </is>
+      </c>
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>foundation</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>opt_ruins_careful</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>谨慎搜寻</t>
+        </is>
+      </c>
+      <c r="C8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
